--- a/healthcare_forms/028_medical_lab_access_form--healthcare_forms.xlsx
+++ b/healthcare_forms/028_medical_lab_access_form--healthcare_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1118,8 +1118,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="35" customWidth="1" min="2" max="2"/>
-    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1147,12 +1147,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'user_1'}</t>
+          <t>user_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'User 1'}</t>
+          <t>User 1</t>
         </is>
       </c>
     </row>
@@ -1164,12 +1164,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'user_2'}</t>
+          <t>user_2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'User 2'}</t>
+          <t>User 2</t>
         </is>
       </c>
     </row>
@@ -1181,12 +1181,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'user_3'}</t>
+          <t>user_3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'User 3'}</t>
+          <t>User 3</t>
         </is>
       </c>
     </row>
@@ -1198,12 +1198,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'access_1'}</t>
+          <t>access_1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Access 1'}</t>
+          <t>Access 1</t>
         </is>
       </c>
     </row>
@@ -1215,12 +1215,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'access_2'}</t>
+          <t>access_2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Access 2'}</t>
+          <t>Access 2</t>
         </is>
       </c>
     </row>
@@ -1232,12 +1232,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'access_3'}</t>
+          <t>access_3</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Access 3'}</t>
+          <t>Access 3</t>
         </is>
       </c>
     </row>
@@ -1249,12 +1249,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'low_level'}</t>
+          <t>low_level</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Low Level'}</t>
+          <t>Low Level</t>
         </is>
       </c>
     </row>
@@ -1266,12 +1266,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'medium_level'}</t>
+          <t>medium_level</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Medium Level'}</t>
+          <t>Medium Level</t>
         </is>
       </c>
     </row>
@@ -1283,12 +1283,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'high_level'}</t>
+          <t>high_level</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'High Level'}</t>
+          <t>High Level</t>
         </is>
       </c>
     </row>
@@ -1300,12 +1300,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'staff_1'}</t>
+          <t>staff_1</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Staff 1'}</t>
+          <t>Staff 1</t>
         </is>
       </c>
     </row>
@@ -1317,12 +1317,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'staff_2'}</t>
+          <t>staff_2</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Staff 2'}</t>
+          <t>Staff 2</t>
         </is>
       </c>
     </row>
@@ -1334,12 +1334,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'staff_3'}</t>
+          <t>staff_3</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Staff 3'}</t>
+          <t>Staff 3</t>
         </is>
       </c>
     </row>
